--- a/templates/excel/Site_Diary_TEMPLATE.xlsx
+++ b/templates/excel/Site_Diary_TEMPLATE.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Weather Summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Instructions" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -787,14 +787,14 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="n">
-        <f aca="false">Setup!B3</f>
+        <f aca="false">Setup!B4</f>
         <v>0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="n">
-        <f aca="false">Setup!B7</f>
+        <f aca="false">Setup!B8</f>
         <v>0</v>
       </c>
     </row>
